--- a/Thesis Forecasting/metadata/overall_metrics/xgboost_validation_testing_metrics.xlsx
+++ b/Thesis Forecasting/metadata/overall_metrics/xgboost_validation_testing_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,57 +444,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>plant</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>feature_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>val_operational_mape</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>val_mae</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>val_rmse</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>val_r2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>test_operational_mape</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>test_mae</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>test_rmse</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>test_r2</t>
         </is>
@@ -503,28 +515,28 @@
         <v>203</v>
       </c>
       <c r="D2" t="n">
-        <v>3.323403899156645</v>
+        <v>3.482055321546861</v>
       </c>
       <c r="E2" t="n">
-        <v>1.645213327941072</v>
+        <v>1.70337171965392</v>
       </c>
       <c r="F2" t="n">
-        <v>2.610490062798169</v>
+        <v>2.685012036042101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9363468546996556</v>
+        <v>0.932660753366213</v>
       </c>
       <c r="H2" t="n">
-        <v>3.370461140997374</v>
+        <v>3.53851452524597</v>
       </c>
       <c r="I2" t="n">
-        <v>1.841917194389731</v>
+        <v>1.924311961185131</v>
       </c>
       <c r="J2" t="n">
-        <v>3.355801362880302</v>
+        <v>3.434939096692335</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9037669556551408</v>
+        <v>0.8991746321461771</v>
       </c>
     </row>
     <row r="3">
@@ -581,28 +593,28 @@
         <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9380442865162972</v>
+        <v>1.089674519802447</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8168637963669958</v>
+        <v>0.9687730133309831</v>
       </c>
       <c r="F4" t="n">
-        <v>3.149836210988566</v>
+        <v>3.177930741186374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9585835968459901</v>
+        <v>0.9578414861573398</v>
       </c>
       <c r="H4" t="n">
-        <v>0.845976033866791</v>
+        <v>0.9933661062084465</v>
       </c>
       <c r="I4" t="n">
-        <v>1.014324090475704</v>
+        <v>1.213445525344139</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92752234014815</v>
+        <v>2.984665718455537</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9505137001947774</v>
+        <v>0.9485629632986261</v>
       </c>
     </row>
     <row r="5">
@@ -620,28 +632,28 @@
         <v>213</v>
       </c>
       <c r="D5" t="n">
-        <v>3.988128446352618</v>
+        <v>4.165805949325734</v>
       </c>
       <c r="E5" t="n">
-        <v>1.41965869703899</v>
+        <v>1.455371341845735</v>
       </c>
       <c r="F5" t="n">
-        <v>2.109692331530161</v>
+        <v>2.162484443380779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9144810276620942</v>
+        <v>0.9101474910001381</v>
       </c>
       <c r="H5" t="n">
-        <v>4.453293729564107</v>
+        <v>4.420950630384259</v>
       </c>
       <c r="I5" t="n">
-        <v>1.742999682415971</v>
+        <v>1.69356783066053</v>
       </c>
       <c r="J5" t="n">
-        <v>2.353061622185304</v>
+        <v>2.31868512464041</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8852162492606863</v>
+        <v>0.8885455630447319</v>
       </c>
     </row>
     <row r="6">
